--- a/Test data/pSHG stack parameters/Test data_pSHG stack parameters.xlsx
+++ b/Test data/pSHG stack parameters/Test data_pSHG stack parameters.xlsx
@@ -409,28 +409,28 @@
         <v>12368817126</v>
       </c>
       <c r="D3">
-        <v>0.2797780448940629</v>
+        <v>0.2866475696697435</v>
       </c>
       <c r="E3">
-        <v>0.07080964971959224</v>
+        <v>0.06942717787944724</v>
       </c>
       <c r="F3">
-        <v>0.08479867880076918</v>
+        <v>0.08356903135845926</v>
       </c>
       <c r="G3">
-        <v>0.04044247578824058</v>
+        <v>0.03892625190837359</v>
       </c>
       <c r="H3">
-        <v>-0.01408804122564487</v>
+        <v>-0.01160905054502784</v>
       </c>
       <c r="I3">
-        <v>0.04586869137153026</v>
+        <v>0.04325092844935657</v>
       </c>
       <c r="J3">
-        <v>-0.06898672552254091</v>
+        <v>-0.06933198366575205</v>
       </c>
       <c r="K3">
-        <v>0.04200990028795456</v>
+        <v>0.04106944441441628</v>
       </c>
     </row>
   </sheetData>
